--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25709-2025 artfynd.xlsx
+++ b/artfynd/A 25709-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210104</v>
       </c>
       <c r="B2" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
